--- a/export/season_plan.xlsx
+++ b/export/season_plan.xlsx
@@ -11,16 +11,16 @@
     <sheet name="06.09 U10 Jarhallen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="26.09 U11 Varner Arena" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="11.10 U10 Sandefjord" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="25.10 U11 Bærum ishall" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="25.10 U11 Baerum ishall" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="14.11 U10 Holmenkollen ishall" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="28.11 U11 Skien ishall" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="13.12 U10 Ringerikshallen" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="09.01 U11 Kongsberghallen" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="16.01 U10 Tønsberghallen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="16.01 U10 Tonsberghallen" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="31.01 U11 Jarhallen" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="14.02 U10 Varner Arena" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="06.03 U11 Sandefjord" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14.03 U10 Bærum ishall" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="14.03 U10 Baerum ishall" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="10.04 U11 Holmenkollen ishall" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="18.04 U10 Skien ishall" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Klubb Jar" sheetId="17" state="visible" r:id="rId17"/>
@@ -603,7 +603,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>16.01.2027 (lørdag) — U10 — Tønsberghallen</t>
+          <t>16.01.2027 (lørdag) — U10 — Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>14.03.2027 (søndag) — U10 — Bærum ishall</t>
+          <t>14.03.2027 (søndag) — U10 — Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bærum ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tønsberghallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>25.10.2026 (søndag) — U11 — Bærum ishall</t>
+          <t>25.10.2026 (søndag) — U11 — Baerum ishall</t>
         </is>
       </c>
     </row>

--- a/export/season_plan.xlsx
+++ b/export/season_plan.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jar 1, Frisk Asker 1, Sandefjord 1, Jutul 1, Holmen 1, Skien 1, Ringerike 1, Kongsberg 1</t>
+          <t>Jar 1, Frisk Asker 1, Sandefjord 1, Jutul 1, Holmen 1, Skien 1, Ringerike 1, Kongsberg 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -561,12 +561,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jar 2, Frisk Asker 2, Ringerike 2, Tønsberg 1, Sandefjord 1, Jutul 1</t>
+          <t>Jar 2, Frisk Asker 2, Ringerike 2, Sandefjord 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tønsberg 1 (~80 km)</t>
+          <t>Ringerike 2 (~55 km)</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jar 3, Frisk Asker 3, Holmen 1, Ringerike 2, Skien 1, Tønsberg 1, Kongsberg 1, Sandefjord 1</t>
+          <t>Jar 3, Frisk Asker 3, Skien 1, Ringerike 2, Kongsberg 1, Tønsberg 1, Sandefjord 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jar 4, Frisk Asker 1, Ringerike 2, Tønsberg 1, Jutul 1, Holmen 1</t>
+          <t>Jar 4, Frisk Asker 1, Ringerike 2, Skien 1, Kongsberg 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jar 5, Frisk Asker 2, Ringerike 1, Skien 1, Tønsberg 1, Kongsberg 1, Jutul 1, Holmen 1</t>
+          <t>Jar 5, Frisk Asker 2, Ringerike 1, Skien 1, Kongsberg 1, Sandefjord 1, Tønsberg 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jar 6, Frisk Asker 3, Ringerike 1, Jutul 1, Sandefjord 1, Skien 1</t>
+          <t>Jar 6, Frisk Asker 3, Ringerike 1, Sandefjord 1, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jar 7, Frisk Asker 1, Ringerike 1, Tønsberg 1, Kongsberg 1, Sandefjord 1, Holmen 1, Skien 1</t>
+          <t>Jar 7, Frisk Asker 1, Ringerike 1, Holmen 1, Kongsberg 1, Tønsberg 1, Sandefjord 1, Jutul 1, Skien 1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jar 1, Frisk Asker 2, Ringerike 2, Kongsberg 1, Sandefjord 1, Jutul 1</t>
+          <t>Jar 1, Frisk Asker 2, Ringerike 2, Kongsberg 1, Holmen 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jar 1 (~80 km)</t>
+          <t>Holmen 1 (~85 km)</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jar 2, Frisk Asker 3, Ringerike 1, Holmen 1, Kongsberg 1, Tønsberg 1, Jutul 1, Skien 1</t>
+          <t>Jar 2, Frisk Asker 3, Ringerike 1, Kongsberg 1, Tønsberg 1, Sandefjord 1, Holmen 1, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jar 3, Frisk Asker 1, Ringerike 1, Jutul 1, Sandefjord 1, Tønsberg 1</t>
+          <t>Jar 3, Frisk Asker 1, Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tønsberg 1 (~100 km)</t>
+          <t>Kongsberg 1 (~80 km)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jar 4, Frisk Asker 2, Skien 1, Ringerike 2, Kongsberg 1, Sandefjord 1, Holmen 1, Tønsberg 1</t>
+          <t>Jar 4, Frisk Asker 2, Ringerike 1, Jutul 1, Tønsberg 1, Skien 1, Holmen 1, Sandefjord 1, Kongsberg 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jar 5, Frisk Asker 3, Ringerike 2, Sandefjord 1, Holmen 1, Jutul 1</t>
+          <t>Jar 5, Frisk Asker 3, Ringerike 2, Jutul 1, Tønsberg 1, Skien 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ringerike 2 (~50 km)</t>
+          <t>Skien 1 (~120 km)</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jar 6, Frisk Asker 1, Ringerike 2, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1, Holmen 1</t>
+          <t>Jar 6, Frisk Asker 1, Ringerike 2, Holmen 1, Jutul 1, Kongsberg 1, Skien 1, Sandefjord 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jar 1, Frisk Asker 3, Tønsberg 1, Ringerike 1, Kongsberg 1, Sandefjord 1</t>
+          <t>Jar 1, Frisk Asker 3, Ringerike 2, Sandefjord 1, Kongsberg 1, Jutul 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tønsberg 1 (~80 km)</t>
+          <t>Kongsberg 1 (~60 km)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jar 7, Frisk Asker 2, Ringerike 1, Holmen 1, Jutul 1, Skien 1, Sandefjord 1, Kongsberg 1</t>
+          <t>Jar 7, Frisk Asker 2, Ringerike 2, Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Jutul 1, Kongsberg 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1078,14 +1078,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 1, Frisk Asker 2, Ringerike 2, Kongsberg 1, Sandefjord 1, Jutul 1</t>
+          <t>Deltakende lag: Jar 1, Frisk Asker 2, Ringerike 2, Kongsberg 1, Holmen 1, Tønsberg 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Jar 1 (~80 km)</t>
+          <t>Lengst reise: Holmen 1 (~85 km)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1413,7 +1413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 2, Frisk Asker 3, Ringerike 1, Holmen 1, Kongsberg 1, Tønsberg 1, Jutul 1, Skien 1</t>
+          <t>Deltakende lag: Jar 2, Frisk Asker 3, Ringerike 1, Kongsberg 1, Tønsberg 1, Sandefjord 1, Holmen 1, Skien 1, Jutul 1</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1939,15 +1939,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 2</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Kongsberg 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Tønsberg 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1982,14 +2126,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 3, Frisk Asker 1, Ringerike 1, Jutul 1, Sandefjord 1, Tønsberg 1</t>
+          <t>Deltakende lag: Jar 3, Frisk Asker 1, Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Tønsberg 1 (~100 km)</t>
+          <t>Lengst reise: Kongsberg 1 (~80 km)</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2171,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2063,7 +2207,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2094,12 +2238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2135,7 +2279,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2166,7 +2310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2207,7 +2351,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2220,7 +2364,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2261,7 +2405,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2274,7 +2418,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2297,7 +2441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2317,7 +2461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 4, Frisk Asker 2, Skien 1, Ringerike 2, Kongsberg 1, Sandefjord 1, Holmen 1, Tønsberg 1</t>
+          <t>Deltakende lag: Jar 4, Frisk Asker 2, Ringerike 1, Jutul 1, Tønsberg 1, Skien 1, Holmen 1, Sandefjord 1, Kongsberg 1</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2375,12 +2519,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2393,12 +2537,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2411,12 +2555,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2429,7 +2573,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2447,12 +2591,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2465,12 +2609,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2483,12 +2627,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2519,12 +2663,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2537,12 +2681,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2555,12 +2699,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2573,7 +2717,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2591,7 +2735,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2609,12 +2753,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2627,12 +2771,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2650,7 +2794,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2663,12 +2807,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2686,7 +2830,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2699,12 +2843,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2717,7 +2861,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2735,12 +2879,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2753,12 +2897,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2771,7 +2915,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2794,7 +2938,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2807,12 +2951,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2825,12 +2969,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2843,15 +2987,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Kongsberg 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 4</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>Sandefjord 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2886,14 +3174,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 5, Frisk Asker 3, Ringerike 2, Sandefjord 1, Holmen 1, Jutul 1</t>
+          <t>Deltakende lag: Jar 5, Frisk Asker 3, Ringerike 2, Jutul 1, Tønsberg 1, Skien 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 2 (~50 km)</t>
+          <t>Lengst reise: Skien 1 (~120 km)</t>
         </is>
       </c>
     </row>
@@ -2931,7 +3219,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2949,7 +3237,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2967,7 +3255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2980,7 +3268,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2998,12 +3286,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3039,7 +3327,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3052,7 +3340,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3070,7 +3358,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3111,7 +3399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3124,12 +3412,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3165,7 +3453,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3178,12 +3466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -3201,7 +3489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3221,7 +3509,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 6, Frisk Asker 1, Ringerike 2, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1, Holmen 1</t>
+          <t>Deltakende lag: Jar 6, Frisk Asker 1, Ringerike 2, Holmen 1, Jutul 1, Kongsberg 1, Skien 1, Sandefjord 1, Tønsberg 1</t>
         </is>
       </c>
     </row>
@@ -3261,12 +3549,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 6</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3279,12 +3567,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3297,12 +3585,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3315,12 +3603,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3351,12 +3639,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -3369,12 +3657,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3387,12 +3675,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3410,7 +3698,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3441,12 +3729,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3459,12 +3747,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3500,7 +3788,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3513,7 +3801,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3531,12 +3819,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3572,7 +3860,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -3585,12 +3873,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3608,7 +3896,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3621,7 +3909,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3639,7 +3927,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3657,7 +3945,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3675,12 +3963,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -3698,7 +3986,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -3711,12 +3999,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3734,7 +4022,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3747,15 +4035,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 6</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Skien 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Jutul 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3790,14 +4222,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 1, Frisk Asker 3, Tønsberg 1, Ringerike 1, Kongsberg 1, Sandefjord 1</t>
+          <t>Deltakende lag: Jar 1, Frisk Asker 3, Ringerike 2, Sandefjord 1, Kongsberg 1, Jutul 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Tønsberg 1 (~80 km)</t>
+          <t>Lengst reise: Kongsberg 1 (~60 km)</t>
         </is>
       </c>
     </row>
@@ -3835,7 +4267,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -3866,12 +4298,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3902,12 +4334,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3920,7 +4352,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3943,7 +4375,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3961,7 +4393,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3974,7 +4406,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3992,7 +4424,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4015,7 +4447,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -4028,7 +4460,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4064,12 +4496,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4082,7 +4514,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4105,7 +4537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4125,7 +4557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 7, Frisk Asker 2, Ringerike 1, Holmen 1, Jutul 1, Skien 1, Sandefjord 1, Kongsberg 1</t>
+          <t>Deltakende lag: Jar 7, Frisk Asker 2, Ringerike 2, Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Jutul 1, Kongsberg 1</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 7</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4183,12 +4615,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4201,12 +4633,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4224,7 +4656,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4237,7 +4669,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4255,12 +4687,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4273,12 +4705,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -4296,7 +4728,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -4314,7 +4746,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -4327,12 +4759,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -4345,7 +4777,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4363,12 +4795,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -4381,7 +4813,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4399,12 +4831,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4417,12 +4849,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4435,12 +4867,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4458,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4471,12 +4903,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4489,12 +4921,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4507,12 +4939,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -4525,7 +4957,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4543,12 +4975,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -4561,12 +4993,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4579,12 +5011,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -4602,7 +5034,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4615,12 +5047,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4633,12 +5065,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4656,10 +5088,154 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Skien 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4748,7 +5324,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Ringerike 1, Skien 1, Holmen 1, Jutul 1, Sandefjord 1, Frisk Asker 1</t>
+          <t>Tønsberg 1, Kongsberg 1, Ringerike 1, Skien 1, Holmen 1, Jutul 1, Sandefjord 1, Frisk Asker 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -4780,7 +5356,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jutul 1, Sandefjord 1, Tønsberg 1, Ringerike 2, Frisk Asker 2</t>
+          <t>Holmen 1, Jutul 1, Sandefjord 1, Ringerike 2, Frisk Asker 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4812,7 +5388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Kongsberg 1, Tønsberg 1, Skien 1, Ringerike 2, Holmen 1, Frisk Asker 3</t>
+          <t>Holmen 1, Jutul 1, Sandefjord 1, Tønsberg 1, Kongsberg 1, Ringerike 2, Skien 1, Frisk Asker 3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4844,7 +5420,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Holmen 1, Jutul 1, Tønsberg 1, Ringerike 2, Frisk Asker 1</t>
+          <t>Tønsberg 1, Kongsberg 1, Skien 1, Ringerike 2, Frisk Asker 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4876,7 +5452,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Holmen 1, Jutul 1, Kongsberg 1, Tønsberg 1, Skien 1, Ringerike 1, Frisk Asker 2</t>
+          <t>Holmen 1, Jutul 1, Tønsberg 1, Sandefjord 1, Kongsberg 1, Skien 1, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4908,7 +5484,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Skien 1, Sandefjord 1, Jutul 1, Ringerike 1, Frisk Asker 3</t>
+          <t>Jutul 1, Skien 1, Sandefjord 1, Ringerike 1, Frisk Asker 3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4940,7 +5516,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skien 1, Holmen 1, Sandefjord 1, Kongsberg 1, Tønsberg 1, Ringerike 1, Frisk Asker 1</t>
+          <t>Skien 1, Jutul 1, Sandefjord 1, Tønsberg 1, Kongsberg 1, Holmen 1, Ringerike 1, Frisk Asker 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4972,7 +5548,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jutul 1, Sandefjord 1, Kongsberg 1, Ringerike 2, Frisk Asker 2</t>
+          <t>Tønsberg 1, Holmen 1, Kongsberg 1, Ringerike 2, Frisk Asker 2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5004,7 +5580,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Skien 1, Jutul 1, Tønsberg 1, Kongsberg 1, Holmen 1, Ringerike 1, Frisk Asker 3</t>
+          <t>Jutul 1, Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Kongsberg 1, Ringerike 1, Frisk Asker 3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5036,7 +5612,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Sandefjord 1, Jutul 1, Ringerike 1, Frisk Asker 1</t>
+          <t>Kongsberg 1, Sandefjord 1, Holmen 1, Ringerike 1, Frisk Asker 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5068,7 +5644,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Holmen 1, Sandefjord 1, Kongsberg 1, Ringerike 2, Skien 1, Frisk Asker 2</t>
+          <t>Kongsberg 1, Sandefjord 1, Holmen 1, Skien 1, Tønsberg 1, Jutul 1, Ringerike 1, Frisk Asker 2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5100,7 +5676,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jutul 1, Holmen 1, Sandefjord 1, Ringerike 2, Frisk Asker 3</t>
+          <t>Skien 1, Tønsberg 1, Jutul 1, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5132,7 +5708,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Holmen 1, Tønsberg 1, Jutul 1, Skien 1, Kongsberg 1, Ringerike 2, Frisk Asker 1</t>
+          <t>Tønsberg 1, Sandefjord 1, Skien 1, Kongsberg 1, Jutul 1, Holmen 1, Ringerike 2, Frisk Asker 1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5164,7 +5740,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Kongsberg 1, Ringerike 1, Tønsberg 1, Frisk Asker 3</t>
+          <t>Jutul 1, Kongsberg 1, Sandefjord 1, Ringerike 2, Frisk Asker 3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5196,7 +5772,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Sandefjord 1, Skien 1, Jutul 1, Holmen 1, Ringerike 1, Frisk Asker 2</t>
+          <t>Kongsberg 1, Jutul 1, Tønsberg 1, Sandefjord 1, Holmen 1, Skien 1, Ringerike 2, Frisk Asker 2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5290,7 +5866,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1, Jar 1</t>
+          <t>Tønsberg 1, Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1, Jar 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5322,7 +5898,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Ringerike 2, Jutul 1, Tønsberg 1, Jar 2</t>
+          <t>Jutul 1, Ringerike 2, Holmen 1, Sandefjord 1, Jar 2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5354,7 +5930,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Ringerike 2, Jar 3</t>
+          <t>Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1, Ringerike 2, Jar 3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5386,7 +5962,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jutul 1, Ringerike 2, Holmen 1, Tønsberg 1, Jar 4</t>
+          <t>Kongsberg 1, Ringerike 2, Tønsberg 1, Skien 1, Jar 4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5418,7 +5994,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jutul 1, Tønsberg 1, Ringerike 1, Holmen 1, Kongsberg 1, Skien 1, Jar 5</t>
+          <t>Holmen 1, Tønsberg 1, Kongsberg 1, Ringerike 1, Jutul 1, Sandefjord 1, Skien 1, Jar 5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5450,7 +6026,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Ringerike 1, Skien 1, Jutul 1, Jar 6</t>
+          <t>Skien 1, Ringerike 1, Jutul 1, Sandefjord 1, Jar 6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5482,7 +6058,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Holmen 1, Kongsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Tønsberg 1, Jar 7</t>
+          <t>Skien 1, Sandefjord 1, Kongsberg 1, Ringerike 1, Jutul 1, Tønsberg 1, Holmen 1, Jar 7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5514,7 +6090,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Ringerike 2, Jutul 1, Kongsberg 1, Jar 1</t>
+          <t>Holmen 1, Ringerike 2, Tønsberg 1, Kongsberg 1, Jar 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5546,7 +6122,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jutul 1, Kongsberg 1, Ringerike 1, Skien 1, Tønsberg 1, Holmen 1, Jar 2</t>
+          <t>Jutul 1, Holmen 1, Tønsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Kongsberg 1, Jar 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5578,7 +6154,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Ringerike 1, Tønsberg 1, Jutul 1, Jar 3</t>
+          <t>Sandefjord 1, Ringerike 1, Kongsberg 1, Holmen 1, Jar 3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -5610,7 +6186,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Holmen 1, Kongsberg 1, Skien 1, Tønsberg 1, Sandefjord 1, Ringerike 2, Jar 4</t>
+          <t>Kongsberg 1, Holmen 1, Tønsberg 1, Ringerike 1, Sandefjord 1, Skien 1, Jutul 1, Jar 4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -5642,7 +6218,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Holmen 1, Ringerike 2, Jutul 1, Sandefjord 1, Jar 5</t>
+          <t>Tønsberg 1, Ringerike 2, Skien 1, Jutul 1, Jar 5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5674,7 +6250,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Skien 1, Ringerike 2, Holmen 1, Jutul 1, Kongsberg 1, Jar 6</t>
+          <t>Tønsberg 1, Skien 1, Jutul 1, Ringerike 2, Sandefjord 1, Kongsberg 1, Holmen 1, Jar 6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5706,7 +6282,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Tønsberg 1, Sandefjord 1, Ringerike 1, Jar 1</t>
+          <t>Kongsberg 1, Ringerike 2, Jutul 1, Sandefjord 1, Jar 1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5738,7 +6314,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Jutul 1, Ringerike 1, Kongsberg 1, Skien 1, Holmen 1, Jar 7</t>
+          <t>Kongsberg 1, Tønsberg 1, Holmen 1, Ringerike 2, Jutul 1, Sandefjord 1, Skien 1, Jar 7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5998,7 +6574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6072,7 +6648,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Skien 1, Jutul 1, Frisk Asker 1, Ringerike 1, Holmen 1, Jar 1, Kongsberg 1</t>
+          <t>Kongsberg 1, Skien 1, Jutul 1, Frisk Asker 1, Tønsberg 1, Ringerike 1, Holmen 1, Jar 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6104,7 +6680,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar 2, Ringerike 2, Jutul 1, Tønsberg 1</t>
+          <t>Ringerike 2, Holmen 1, Jar 2, Frisk Asker 2, Jutul 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6136,7 +6712,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jar 3, Tønsberg 1, Ringerike 2, Frisk Asker 3, Kongsberg 1, Skien 1, Holmen 1</t>
+          <t>Ringerike 2, Frisk Asker 3, Holmen 1, Jar 3, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6153,12 +6729,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28.11.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6168,12 +6744,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar 6, Ringerike 1, Skien 1, Jutul 1</t>
+          <t>Kongsberg 1, Ringerike 1, Jutul 1, Jar 5, Skien 1, Frisk Asker 2, Holmen 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -6185,27 +6761,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>28.11.2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ringerike 1, Skien 1, Jar 7, Tønsberg 1, Frisk Asker 1, Holmen 1, Kongsberg 1</t>
+          <t>Ringerike 1, Jutul 1, Jar 6, Frisk Asker 3, Skien 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Holmenkollen ishall</t>
         </is>
       </c>
     </row>
@@ -6217,27 +6793,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar 1, Ringerike 2, Jutul 1, Kongsberg 1</t>
+          <t>Holmen 1, Frisk Asker 1, Skien 1, Jar 7, Kongsberg 1, Ringerike 1, Jutul 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
     </row>
@@ -6249,27 +6825,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar 3, Ringerike 1, Tønsberg 1, Jutul 1</t>
+          <t>Tønsberg 1, Ringerike 1, Skien 1, Jar 2, Kongsberg 1, Frisk Asker 3, Jutul 1, Holmen 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -6281,12 +6857,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6296,7 +6872,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Skien 1, Tønsberg 1, Jar 4, Ringerike 2, Frisk Asker 2, Holmen 1, Kongsberg 1</t>
+          <t>Frisk Asker 1, Jar 3, Ringerike 1, Kongsberg 1, Holmen 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6313,22 +6889,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>06.03.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jutul 1, Jar 5, Frisk Asker 3, Holmen 1</t>
+          <t>Ringerike 1, Jar 4, Skien 1, Jutul 1, Frisk Asker 2, Kongsberg 1, Holmen 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6345,27 +6921,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jar 1, Ringerike 1, Frisk Asker 3, Kongsberg 1, Tønsberg 1</t>
+          <t>Ringerike 2, Jar 6, Kongsberg 1, Holmen 1, Frisk Asker 1, Tønsberg 1, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
     </row>
@@ -6377,25 +6953,57 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ringerike 2, Jutul 1, Jar 1, Frisk Asker 3, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>U10</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>18.04.2027</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>søndag</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Frisk Asker 2, Jar 7, Jutul 1, Ringerike 1, Kongsberg 1, Skien 1, Holmen 1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Holmen 1, Ringerike 2, Jutul 1, Jar 7, Skien 1, Frisk Asker 2, Kongsberg 1, Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Ringerikshallen</t>
         </is>
@@ -6407,6 +7015,866 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Klubb: Jutul</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Lag</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Aldersgruppe</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Ukedag</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Motstander(e)</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Vertsarena</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jar 1, Frisk Asker 1, Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2, Jar 2, Ringerike 2, Holmen 1, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11.10.2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Skien 1, Jar 3, Tønsberg 1, Ringerike 2, Frisk Asker 3, Holmen 1, Sandefjord 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14.11.2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ringerike 1, Jar 5, Sandefjord 1, Skien 1, Frisk Asker 2, Holmen 1, Tønsberg 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Baerum ishall</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>28.11.2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jar 6, Sandefjord 1, Frisk Asker 3, Skien 1, Ringerike 1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Holmenkollen ishall</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13.12.2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ringerike 1, Jar 7, Tønsberg 1, Holmen 1, Frisk Asker 1, Skien 1, Sandefjord 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skien ishall</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16.01.2027</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3, Jar 2, Holmen 1, Tønsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tonsberghallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14.02.2027</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Holmen 1, Tønsberg 1, Ringerike 1, Sandefjord 1, Skien 1, Jar 4, Frisk Asker 2, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>06.03.2027</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ringerike 2, Skien 1, Jar 5, Frisk Asker 3, Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kongsberg 1, Holmen 1, Frisk Asker 1, Tønsberg 1, Skien 1, Jar 6, Ringerike 2, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Jar 1, Sandefjord 1, Frisk Asker 3, Kongsberg 1, Ringerike 2</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ringerike 2, Jar 7, Sandefjord 1, Skien 1, Frisk Asker 2, Kongsberg 1, Tønsberg 1, Holmen 1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Klubb: Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Lag</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Aldersgruppe</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Ukedag</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Motstander(e)</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Vertsarena</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Skien 1, Jutul 1, Frisk Asker 1, Tønsberg 1, Ringerike 1, Jar 1, Sandefjord 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>26.09.2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Jar 2, Sandefjord 1, Frisk Asker 2, Jutul 1, Ringerike 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11.10.2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3, Jar 3, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1, Ringerike 2</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14.11.2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2, Jar 5, Tønsberg 1, Kongsberg 1, Ringerike 1, Jutul 1, Sandefjord 1, Skien 1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Baerum ishall</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13.12.2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sandefjord 1, Kongsberg 1, Ringerike 1, Jutul 1, Tønsberg 1, Jar 7, Frisk Asker 1, Skien 1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skien ishall</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>09.01.2027</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2, Jar 1, Ringerike 2, Tønsberg 1, Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kongsberghallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16.01.2027</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kongsberg 1, Frisk Asker 3, Jutul 1, Jar 2, Tønsberg 1, Ringerike 1, Skien 1, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tonsberghallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>31.01.2027</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ringerike 1, Kongsberg 1, Jar 3, Frisk Asker 1, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14.02.2027</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jutul 1, Frisk Asker 2, Kongsberg 1, Jar 4, Tønsberg 1, Ringerike 1, Sandefjord 1, Skien 1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Skien 1, Jutul 1, Ringerike 2, Sandefjord 1, Kongsberg 1, Jar 6, Frisk Asker 1, Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sandefjord 1, Skien 1, Frisk Asker 2, Kongsberg 1, Tønsberg 1, Jar 7, Ringerike 2, Jutul 1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6426,7 +7894,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Klubb: Jutul</t>
+          <t>Klubb: Skien</t>
         </is>
       </c>
     </row>
@@ -6466,7 +7934,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6486,7 +7954,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jar 1, Frisk Asker 1, Ringerike 1</t>
+          <t>Holmen 1, Sandefjord 1, Kongsberg 1, Jar 1, Jutul 1, Frisk Asker 1, Tønsberg 1, Ringerike 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -6498,39 +7966,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>11.10.2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jar 2, Tønsberg 1, Frisk Asker 2, Sandefjord 1, Ringerike 2</t>
+          <t>Jutul 1, Tønsberg 1, Ringerike 2, Frisk Asker 3, Holmen 1, Sandefjord 1, Kongsberg 1, Jar 3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Ringerikshallen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6550,7 +8018,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar 4, Ringerike 2, Holmen 1, Tønsberg 1</t>
+          <t>Ringerike 2, Tønsberg 1, Jar 4, Frisk Asker 1, Kongsberg 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -6562,7 +8030,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6582,7 +8050,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Frisk Asker 2, Jar 5, Tønsberg 1, Ringerike 1, Holmen 1, Kongsberg 1, Skien 1</t>
+          <t>Tønsberg 1, Kongsberg 1, Ringerike 1, Jutul 1, Sandefjord 1, Jar 5, Frisk Asker 2, Holmen 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -6594,7 +8062,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6614,7 +8082,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ringerike 1, Skien 1, Jar 6, Frisk Asker 3, Sandefjord 1</t>
+          <t>Frisk Asker 3, Jar 6, Ringerike 1, Jutul 1, Sandefjord 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -6626,39 +8094,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jar 1, Kongsberg 1, Frisk Asker 2, Sandefjord 1, Ringerike 2</t>
+          <t>Frisk Asker 1, Jar 7, Sandefjord 1, Kongsberg 1, Ringerike 1, Jutul 1, Tønsberg 1, Holmen 1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6678,7 +8146,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar 2, Kongsberg 1, Ringerike 1, Skien 1, Tønsberg 1, Holmen 1</t>
+          <t>Ringerike 1, Jar 2, Sandefjord 1, Kongsberg 1, Frisk Asker 3, Jutul 1, Holmen 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6690,17 +8158,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6710,7 +8178,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ringerike 1, Tønsberg 1, Jar 3, Frisk Asker 1, Sandefjord 1</t>
+          <t>Tønsberg 1, Ringerike 1, Sandefjord 1, Jar 4, Jutul 1, Frisk Asker 2, Kongsberg 1, Holmen 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6722,7 +8190,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6742,7 +8210,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jar 5, Sandefjord 1, Frisk Asker 3, Holmen 1, Ringerike 2</t>
+          <t>Jar 5, Jutul 1, Frisk Asker 3, Tønsberg 1, Ringerike 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6754,7 +8222,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6774,7 +8242,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ringerike 2, Holmen 1, Jar 6, Kongsberg 1, Frisk Asker 1, Tønsberg 1, Skien 1</t>
+          <t>Holmen 1, Frisk Asker 1, Tønsberg 1, Jar 6, Jutul 1, Ringerike 2, Sandefjord 1, Kongsberg 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6786,7 +8254,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6806,742 +8274,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Holmen 1, Frisk Asker 2, Sandefjord 1, Jar 7, Ringerike 1, Kongsberg 1, Skien 1</t>
+          <t>Tønsberg 1, Holmen 1, Ringerike 2, Jutul 1, Sandefjord 1, Jar 7, Frisk Asker 2, Kongsberg 1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>Ringerikshallen</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Klubb: Holmen</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Aldersgruppe</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Ukedag</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Motstander(e)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Vertsarena</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>06.09.2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jutul 1, Frisk Asker 1, Ringerike 1, Jar 1, Sandefjord 1, Kongsberg 1, Skien 1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>11.10.2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Tønsberg 1, Ringerike 2, Frisk Asker 3, Kongsberg 1, Skien 1, Jar 3, Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ringerikshallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>U11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>25.10.2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Jar 4, Tønsberg 1, Frisk Asker 1, Jutul 1, Ringerike 2</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Sandefjord</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>14.11.2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Jar 5, Kongsberg 1, Skien 1, Frisk Asker 2, Jutul 1, Tønsberg 1, Ringerike 1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Baerum ishall</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>13.12.2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Frisk Asker 1, Jar 7, Kongsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skien ishall</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>16.01.2027</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Kongsberg 1, Ringerike 1, Skien 1, Tønsberg 1, Jar 2, Frisk Asker 3, Jutul 1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14.02.2027</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Frisk Asker 2, Jar 4, Kongsberg 1, Skien 1, Tønsberg 1, Sandefjord 1, Ringerike 2</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>U11</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>06.03.2027</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3, Jar 5, Ringerike 2, Jutul 1, Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Jar 6, Jutul 1, Kongsberg 1, Frisk Asker 1, Tønsberg 1, Skien 1, Ringerike 2</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Jutul 1, Ringerike 1, Kongsberg 1, Skien 1, Jar 7, Frisk Asker 2, Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ringerikshallen</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Klubb: Skien</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Aldersgruppe</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Ukedag</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Motstander(e)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Vertsarena</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>06.09.2026</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sandefjord 1, Kongsberg 1, Jar 1, Jutul 1, Frisk Asker 1, Ringerike 1, Holmen 1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>11.10.2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ringerike 2, Frisk Asker 3, Kongsberg 1, Jar 3, Holmen 1, Sandefjord 1, Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ringerikshallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>14.11.2026</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Tønsberg 1, Ringerike 1, Holmen 1, Kongsberg 1, Jar 5, Frisk Asker 2, Jutul 1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Baerum ishall</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>U11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>28.11.2026</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Jar 6, Jutul 1, Frisk Asker 3, Sandefjord 1, Ringerike 1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Holmenkollen ishall</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>13.12.2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Jar 7, Sandefjord 1, Tønsberg 1, Frisk Asker 1, Holmen 1, Kongsberg 1, Ringerike 1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skien ishall</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>16.01.2027</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>lørdag</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Jar 2, Tønsberg 1, Holmen 1, Frisk Asker 3, Jutul 1, Kongsberg 1, Ringerike 1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tonsberghallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14.02.2027</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sandefjord 1, Ringerike 2, Frisk Asker 2, Holmen 1, Kongsberg 1, Jar 4, Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>14.03.2027</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kongsberg 1, Frisk Asker 1, Tønsberg 1, Jar 6, Ringerike 2, Holmen 1, Jutul 1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Jarhallen</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>18.04.2027</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>søndag</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Ringerike 1, Kongsberg 1, Jar 7, Holmen 1, Frisk Asker 2, Sandefjord 1, Jutul 1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>Ringerikshallen</t>
         </is>
@@ -7632,7 +8368,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1</t>
+          <t>Jutul 1, Frisk Asker 1, Tønsberg 1, Jar 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7664,7 +8400,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Frisk Asker 2, Sandefjord 1, Jar 2, Jutul 1</t>
+          <t>Sandefjord 1, Frisk Asker 2, Jutul 1, Jar 2, Holmen 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7696,7 +8432,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Jar 3, Frisk Asker 3, Kongsberg 1</t>
+          <t>Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1, Tønsberg 1, Jar 3, Frisk Asker 3, Holmen 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7728,7 +8464,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Frisk Asker 1, Jutul 1, Jar 4, Holmen 1</t>
+          <t>Skien 1, Frisk Asker 1, Kongsberg 1, Jar 4, Tønsberg 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7760,7 +8496,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Skien 1, Frisk Asker 2, Jutul 1, Tønsberg 1, Jar 5, Holmen 1</t>
+          <t>Jutul 1, Sandefjord 1, Skien 1, Frisk Asker 2, Holmen 1, Tønsberg 1, Kongsberg 1, Jar 5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7792,7 +8528,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jutul 1, Frisk Asker 3, Sandefjord 1, Jar 6, Skien 1</t>
+          <t>Sandefjord 1, Frisk Asker 3, Skien 1, Jar 6, Jutul 1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7824,7 +8560,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Tønsberg 1, Frisk Asker 1, Holmen 1, Kongsberg 1, Jar 7, Skien 1</t>
+          <t>Jutul 1, Tønsberg 1, Holmen 1, Frisk Asker 1, Skien 1, Sandefjord 1, Kongsberg 1, Jar 7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7856,7 +8592,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Frisk Asker 2, Sandefjord 1, Jar 1, Jutul 1</t>
+          <t>Kongsberg 1, Frisk Asker 2, Holmen 1, Jar 1, Tønsberg 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7888,7 +8624,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Holmen 1, Frisk Asker 3, Jutul 1, Kongsberg 1, Jar 2, Skien 1</t>
+          <t>Skien 1, Sandefjord 1, Kongsberg 1, Frisk Asker 3, Jutul 1, Holmen 1, Tønsberg 1, Jar 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7920,7 +8656,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jutul 1, Frisk Asker 1, Sandefjord 1, Jar 3, Tønsberg 1</t>
+          <t>Holmen 1, Frisk Asker 1, Sandefjord 1, Jar 3, Kongsberg 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7932,7 +8668,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7952,7 +8688,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Skien 1, Tønsberg 1, Sandefjord 1, Jar 4, Frisk Asker 2, Holmen 1</t>
+          <t>Sandefjord 1, Skien 1, Jutul 1, Frisk Asker 2, Kongsberg 1, Holmen 1, Tønsberg 1, Jar 4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7984,7 +8720,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sandefjord 1, Frisk Asker 3, Holmen 1, Jar 5, Jutul 1</t>
+          <t>Jutul 1, Frisk Asker 3, Tønsberg 1, Jar 5, Skien 1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8016,7 +8752,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jutul 1, Kongsberg 1, Frisk Asker 1, Tønsberg 1, Skien 1, Jar 6, Holmen 1</t>
+          <t>Sandefjord 1, Kongsberg 1, Holmen 1, Frisk Asker 1, Tønsberg 1, Skien 1, Jutul 1, Jar 6</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8028,7 +8764,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8048,7 +8784,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Sandefjord 1, Jar 1, Frisk Asker 3, Kongsberg 1</t>
+          <t>Sandefjord 1, Frisk Asker 3, Kongsberg 1, Jar 1, Jutul 1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8060,7 +8796,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8080,7 +8816,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skien 1, Holmen 1, Frisk Asker 2, Sandefjord 1, Jutul 1, Jar 7, Kongsberg 1</t>
+          <t>Jutul 1, Sandefjord 1, Skien 1, Frisk Asker 2, Kongsberg 1, Tønsberg 1, Holmen 1, Jar 7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8100,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8174,7 +8910,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jar 1, Skien 1, Jutul 1, Frisk Asker 1, Ringerike 1, Holmen 1, Sandefjord 1</t>
+          <t>Sandefjord 1, Jar 1, Skien 1, Jutul 1, Frisk Asker 1, Tønsberg 1, Ringerike 1, Holmen 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -8206,7 +8942,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar 3, Skien 1, Holmen 1, Sandefjord 1, Tønsberg 1, Ringerike 2</t>
+          <t>Tønsberg 1, Ringerike 2, Frisk Asker 3, Holmen 1, Sandefjord 1, Jar 3, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8223,27 +8959,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14.11.2026</t>
+          <t>25.10.2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ringerike 1, Holmen 1, Jar 5, Skien 1, Frisk Asker 2, Jutul 1, Tønsberg 1</t>
+          <t>Frisk Asker 1, Jar 4, Ringerike 2, Tønsberg 1, Skien 1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Sandefjord</t>
         </is>
       </c>
     </row>
@@ -8260,22 +8996,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13.12.2026</t>
+          <t>14.11.2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tønsberg 1, Frisk Asker 1, Holmen 1, Jar 7, Ringerike 1, Skien 1, Sandefjord 1</t>
+          <t>Sandefjord 1, Skien 1, Frisk Asker 2, Holmen 1, Tønsberg 1, Jar 5, Ringerike 1, Jutul 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skien ishall</t>
+          <t>Baerum ishall</t>
         </is>
       </c>
     </row>
@@ -8287,27 +9023,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>09.01.2027</t>
+          <t>13.12.2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jutul 1, Jar 1, Frisk Asker 2, Sandefjord 1</t>
+          <t>Tønsberg 1, Holmen 1, Frisk Asker 1, Skien 1, Sandefjord 1, Jar 7, Ringerike 1, Jutul 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Skien ishall</t>
         </is>
       </c>
     </row>
@@ -8319,12 +9055,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8334,12 +9070,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Holmen 1, Frisk Asker 3, Jutul 1, Jar 2, Ringerike 1, Skien 1, Tønsberg 1</t>
+          <t>Ringerike 2, Tønsberg 1, Jar 1, Frisk Asker 2, Holmen 1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
     </row>
@@ -8356,22 +9092,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.02.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ringerike 2, Frisk Asker 2, Holmen 1, Jar 4, Skien 1, Tønsberg 1, Sandefjord 1</t>
+          <t>Holmen 1, Tønsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Jar 2, Frisk Asker 3, Jutul 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -8383,12 +9119,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>31.01.2027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8398,7 +9134,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Skien 1, Ringerike 2, Holmen 1, Jutul 1, Jar 6, Frisk Asker 1, Tønsberg 1</t>
+          <t>Jar 3, Holmen 1, Frisk Asker 1, Sandefjord 1, Ringerike 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8415,27 +9151,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.02.2027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Frisk Asker 3, Jar 1, Tønsberg 1, Sandefjord 1, Ringerike 1</t>
+          <t>Frisk Asker 2, Jar 4, Holmen 1, Tønsberg 1, Ringerike 1, Sandefjord 1, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
     </row>
@@ -8452,20 +9188,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>14.03.2027</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Jutul 1, Ringerike 2, Sandefjord 1, Jar 6, Holmen 1, Frisk Asker 1, Tønsberg 1, Skien 1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.04.2027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>lørdag</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3, Jar 1, Ringerike 2, Jutul 1, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Varner Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>18.04.2027</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>søndag</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Jar 7, Skien 1, Holmen 1, Frisk Asker 2, Sandefjord 1, Jutul 1, Ringerike 1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2, Jar 7, Tønsberg 1, Holmen 1, Ringerike 2, Jutul 1, Sandefjord 1, Skien 1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Ringerikshallen</t>
         </is>
@@ -8482,7 +9282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8541,27 +9341,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ringerike 2, Jutul 1, Jar 2, Frisk Asker 2, Sandefjord 1</t>
+          <t>Frisk Asker 1, Jar 1, Ringerike 1, Holmen 1, Sandefjord 1, Kongsberg 1, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
         </is>
       </c>
     </row>
@@ -8588,7 +9388,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Holmen 1, Sandefjord 1, Jar 3, Ringerike 2, Frisk Asker 3, Kongsberg 1, Skien 1</t>
+          <t>Kongsberg 1, Skien 1, Jutul 1, Jar 3, Ringerike 2, Frisk Asker 3, Holmen 1, Sandefjord 1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8620,7 +9420,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ringerike 2, Holmen 1, Jar 4, Frisk Asker 1, Jutul 1</t>
+          <t>Jar 4, Skien 1, Frisk Asker 1, Kongsberg 1, Ringerike 2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8652,7 +9452,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Skien 1, Frisk Asker 2, Jutul 1, Jar 5, Ringerike 1, Holmen 1, Kongsberg 1</t>
+          <t>Skien 1, Frisk Asker 2, Holmen 1, Jar 5, Kongsberg 1, Ringerike 1, Jutul 1, Sandefjord 1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8684,7 +9484,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kongsberg 1, Ringerike 1, Skien 1, Sandefjord 1, Jar 7, Frisk Asker 1, Holmen 1</t>
+          <t>Kongsberg 1, Ringerike 1, Jutul 1, Jar 7, Holmen 1, Frisk Asker 1, Skien 1, Sandefjord 1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8701,12 +9501,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16.01.2027</t>
+          <t>09.01.2027</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8716,12 +9516,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ringerike 1, Skien 1, Jar 2, Holmen 1, Frisk Asker 3, Jutul 1, Kongsberg 1</t>
+          <t>Jar 1, Kongsberg 1, Frisk Asker 2, Holmen 1, Ringerike 2</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Kongsberghallen</t>
         </is>
       </c>
     </row>
@@ -8733,27 +9533,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>31.01.2027</t>
+          <t>16.01.2027</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jar 3, Jutul 1, Frisk Asker 1, Sandefjord 1, Ringerike 1</t>
+          <t>Sandefjord 1, Kongsberg 1, Frisk Asker 3, Jutul 1, Holmen 1, Jar 2, Ringerike 1, Skien 1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -8780,7 +9580,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jar 4, Sandefjord 1, Ringerike 2, Frisk Asker 2, Holmen 1, Kongsberg 1, Skien 1</t>
+          <t>Skien 1, Jutul 1, Frisk Asker 2, Kongsberg 1, Holmen 1, Jar 4, Ringerike 1, Sandefjord 1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8797,22 +9597,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14.03.2027</t>
+          <t>06.03.2027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>søndag</t>
+          <t>lørdag</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Frisk Asker 1, Jar 6, Skien 1, Ringerike 2, Holmen 1, Jutul 1, Kongsberg 1</t>
+          <t>Frisk Asker 3, Jar 5, Ringerike 2, Skien 1, Jutul 1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8829,27 +9629,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10.04.2027</t>
+          <t>14.03.2027</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lørdag</t>
+          <t>søndag</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ringerike 1, Frisk Asker 3, Kongsberg 1, Jar 1, Sandefjord 1</t>
+          <t>Frisk Asker 1, Jar 6, Skien 1, Jutul 1, Ringerike 2, Sandefjord 1, Kongsberg 1, Holmen 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Varner Arena</t>
+          <t>Jarhallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>18.04.2027</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>søndag</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Skien 1, Frisk Asker 2, Kongsberg 1, Jar 7, Holmen 1, Ringerike 2, Jutul 1, Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ringerikshallen</t>
         </is>
       </c>
     </row>
@@ -8864,7 +9696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -8884,7 +9716,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 1, Frisk Asker 1, Sandefjord 1, Jutul 1, Holmen 1, Skien 1, Ringerike 1, Kongsberg 1</t>
+          <t>Deltakende lag: Jar 1, Frisk Asker 1, Sandefjord 1, Jutul 1, Holmen 1, Skien 1, Ringerike 1, Kongsberg 1, Tønsberg 1</t>
         </is>
       </c>
     </row>
@@ -8924,12 +9756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -8942,12 +9774,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -8960,12 +9792,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -8978,12 +9810,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -8996,7 +9828,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9014,12 +9846,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9032,12 +9864,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -9050,12 +9882,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Jutul 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -9073,7 +9905,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9086,12 +9918,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -9104,12 +9936,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -9122,12 +9954,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -9140,7 +9972,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9158,12 +9990,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -9176,12 +10008,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -9194,12 +10026,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -9217,7 +10049,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -9230,12 +10062,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -9248,12 +10080,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -9266,12 +10098,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -9284,7 +10116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9302,12 +10134,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -9320,12 +10152,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -9338,12 +10170,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -9361,7 +10193,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -9374,12 +10206,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -9392,12 +10224,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -9410,15 +10242,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Holmen 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Skien 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9453,14 +10429,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 2, Frisk Asker 2, Ringerike 2, Tønsberg 1, Sandefjord 1, Jutul 1</t>
+          <t>Deltakende lag: Jar 2, Frisk Asker 2, Ringerike 2, Sandefjord 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Tønsberg 1 (~80 km)</t>
+          <t>Lengst reise: Ringerike 2 (~55 km)</t>
         </is>
       </c>
     </row>
@@ -9498,7 +10474,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -9516,7 +10492,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9534,7 +10510,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9547,7 +10523,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9565,12 +10541,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9606,7 +10582,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -9619,7 +10595,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9637,7 +10613,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9678,7 +10654,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -9691,12 +10667,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Jutul 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -9732,7 +10708,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -9745,12 +10721,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -9768,7 +10744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9788,7 +10764,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 3, Frisk Asker 3, Holmen 1, Ringerike 2, Skien 1, Tønsberg 1, Kongsberg 1, Sandefjord 1</t>
+          <t>Deltakende lag: Jar 3, Frisk Asker 3, Skien 1, Ringerike 2, Kongsberg 1, Tønsberg 1, Sandefjord 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
     </row>
@@ -9828,12 +10804,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 3</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -9846,12 +10822,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9864,12 +10840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9882,12 +10858,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -9900,7 +10876,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9918,12 +10894,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9936,12 +10912,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -9954,12 +10930,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -9977,7 +10953,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9990,12 +10966,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10008,12 +10984,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10026,12 +11002,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10044,7 +11020,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10062,12 +11038,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10080,12 +11056,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Holmen 1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10098,12 +11074,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10121,7 +11097,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10134,12 +11110,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10152,12 +11128,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10170,12 +11146,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -10188,7 +11164,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10206,12 +11182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -10224,12 +11200,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>Sandefjord 1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -10242,12 +11218,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -10265,7 +11241,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -10278,12 +11254,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -10296,12 +11272,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -10314,15 +11290,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Skien 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 3</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Tønsberg 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10357,7 +11477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 4, Frisk Asker 1, Ringerike 2, Tønsberg 1, Jutul 1, Holmen 1</t>
+          <t>Deltakende lag: Jar 4, Frisk Asker 1, Ringerike 2, Skien 1, Kongsberg 1, Tønsberg 1</t>
         </is>
       </c>
     </row>
@@ -10395,7 +11515,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10413,7 +11533,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10431,7 +11551,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -10444,7 +11564,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10462,12 +11582,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10503,7 +11623,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10516,7 +11636,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -10534,7 +11654,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10575,7 +11695,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10588,12 +11708,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10629,7 +11749,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10642,12 +11762,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10665,7 +11785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -10685,7 +11805,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 5, Frisk Asker 2, Ringerike 1, Skien 1, Tønsberg 1, Kongsberg 1, Jutul 1, Holmen 1</t>
+          <t>Deltakende lag: Jar 5, Frisk Asker 2, Ringerike 1, Skien 1, Kongsberg 1, Sandefjord 1, Tønsberg 1, Jutul 1, Holmen 1</t>
         </is>
       </c>
     </row>
@@ -10725,7 +11845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 5</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -10743,7 +11863,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10761,12 +11881,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10779,12 +11899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10797,7 +11917,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10815,12 +11935,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10833,12 +11953,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10851,12 +11971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10874,7 +11994,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10887,7 +12007,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10905,12 +12025,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10923,12 +12043,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10959,12 +12079,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10977,12 +12097,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10995,12 +12115,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -11018,7 +12138,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -11036,7 +12156,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -11049,12 +12169,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -11067,12 +12187,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -11085,7 +12205,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11103,12 +12223,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -11121,7 +12241,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11139,12 +12259,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>Jutul 1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -11162,7 +12282,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -11175,12 +12295,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -11193,12 +12313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -11211,15 +12331,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 5</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Tønsberg 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Kongsberg 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11254,7 +12518,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 6, Frisk Asker 3, Ringerike 1, Jutul 1, Sandefjord 1, Skien 1</t>
+          <t>Deltakende lag: Jar 6, Frisk Asker 3, Ringerike 1, Sandefjord 1, Skien 1, Jutul 1</t>
         </is>
       </c>
     </row>
@@ -11299,7 +12563,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11317,7 +12581,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11335,7 +12599,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11348,7 +12612,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11366,12 +12630,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Jutul 1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -11407,7 +12671,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11420,7 +12684,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11438,7 +12702,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11479,7 +12743,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -11492,12 +12756,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Skien 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -11533,7 +12797,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -11546,12 +12810,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jutul 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -11569,7 +12833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11589,7 +12853,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deltakende lag: Jar 7, Frisk Asker 1, Ringerike 1, Tønsberg 1, Kongsberg 1, Sandefjord 1, Holmen 1, Skien 1</t>
+          <t>Deltakende lag: Jar 7, Frisk Asker 1, Ringerike 1, Holmen 1, Kongsberg 1, Tønsberg 1, Sandefjord 1, Jutul 1, Skien 1</t>
         </is>
       </c>
     </row>
@@ -11629,7 +12893,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar 7</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11647,12 +12911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11665,7 +12929,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11683,12 +12947,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11701,7 +12965,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11724,7 +12988,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -11737,12 +13001,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11755,12 +13019,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -11778,7 +13042,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -11791,12 +13055,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -11809,12 +13073,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -11827,12 +13091,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -11845,7 +13109,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11868,7 +13132,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -11881,12 +13145,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -11899,12 +13163,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Frisk Asker 1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -11935,12 +13199,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Kongsberg 1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -11953,12 +13217,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -11971,12 +13235,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -11989,7 +13253,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12007,7 +13271,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12025,12 +13289,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Sandefjord 1</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -12043,12 +13307,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sandefjord 1</t>
+          <t>Jutul 1</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -12066,7 +13330,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen 1</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -12079,12 +13343,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Skien 1</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -12102,7 +13366,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmen 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -12115,15 +13379,159 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Kongsberg 1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sandefjord 1</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D42" t="n">
         <v>1</v>
       </c>
     </row>

--- a/export/season_plan.xlsx
+++ b/export/season_plan.xlsx
@@ -9,21 +9,21 @@
   <sheets>
     <sheet name="Sesongoversikt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Regler og avgjørelser" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="06.09 U10 Jarhallen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="06.09 U10 Varner Arena" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="26.09 U11 Varner Arena" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="11.10 U10 Ringerikshallen" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="25.10 U11 Sandefjord" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="14.11 U10 Baerum ishall" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="28.11 U11 Holmenkollen ishall" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="25.10 U11 Sandefjord ishall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="14.11 U10 Varner Arena" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="28.11 U11 Varner Arena" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="13.12 U10 Skien ishall" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09.01 U11 Kongsberghallen" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="16.01 U10 Tonsberghallen" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="09.01 U11 Varner Arena" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="16.01 U10 Varner Arena" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="31.01 U11 Jarhallen" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="14.02 U10 Jarhallen" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="06.03 U11 Jarhallen" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="06.03 U11 Varner Arena" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="14.03 U10 Jarhallen" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="10.04 U11 Varner Arena" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="18.04 U10 Ringerikshallen" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18.04 U10 Tonsberghallen" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Klubb Jar" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Klubb Frisk Asker" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Klubb Sandefjord" sheetId="20" state="visible" r:id="rId20"/>
@@ -447,16 +447,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,6 +497,16 @@
           <t>Lengste reise</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Starttid</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sluttid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,12 +526,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -529,9 +541,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skien 1 (~120 km)</t>
-        </is>
-      </c>
+          <t>Skien 1 (~100 km)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +583,8 @@
           <t>Ringerike 2 (~55 km)</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -606,6 +622,8 @@
           <t>Skien 1 (~150 km)</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,12 +643,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -638,7 +656,13 @@
           <t>Jar 4, Frisk Asker 1, Ringerike 2, Skien 1, Kongsberg 1, Tønsberg 1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ringerike 2 (~140 km)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,12 +682,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -673,9 +697,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skien 1 (~120 km)</t>
-        </is>
-      </c>
+          <t>Skien 1 (~100 km)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -695,12 +721,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -710,9 +736,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skien 1 (~130 km)</t>
-        </is>
-      </c>
+          <t>Skien 1 (~100 km)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -750,6 +778,8 @@
           <t>Ringerike 1 (~150 km)</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -769,12 +799,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -784,9 +814,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Holmen 1 (~85 km)</t>
-        </is>
-      </c>
+          <t>Tønsberg 1 (~80 km)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -806,12 +838,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -821,9 +853,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ringerike 1 (~120 km)</t>
-        </is>
-      </c>
+          <t>Skien 1 (~100 km)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -861,6 +895,8 @@
           <t>Kongsberg 1 (~80 km)</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -898,6 +934,8 @@
           <t>Skien 1 (~120 km)</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -917,12 +955,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -932,9 +970,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skien 1 (~120 km)</t>
-        </is>
-      </c>
+          <t>Skien 1 (~100 km)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -972,6 +1012,8 @@
           <t>Skien 1 (~120 km)</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1009,6 +1051,8 @@
           <t>Kongsberg 1 (~60 km)</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1028,12 +1072,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1043,9 +1087,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skien 1 (~150 km)</t>
-        </is>
-      </c>
+          <t>Ringerike 2 (~120 km)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1070,7 +1116,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>09.01.2027 (lørdag) — U11 — Kongsberghallen</t>
+          <t>09.01.2027 (lørdag) — U11 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1131,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Holmen 1 (~85 km)</t>
+          <t>Lengst reise: Tønsberg 1 (~80 km)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1132,7 +1178,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1150,7 +1196,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1168,7 +1214,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1186,7 +1232,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1204,7 +1250,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1222,7 +1268,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1240,7 +1286,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1258,7 +1304,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1276,7 +1322,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1294,7 +1340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1312,7 +1358,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1330,7 +1376,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1348,7 +1394,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1366,7 +1412,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1393,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1405,7 +1451,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>16.01.2027 (lørdag) — U10 — Tonsberghallen</t>
+          <t>16.01.2027 (lørdag) — U10 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~100 km)</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1495,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1467,7 +1513,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1485,7 +1531,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1503,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1521,7 +1567,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1539,7 +1585,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1557,7 +1603,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1575,7 +1621,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1593,7 +1639,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1611,7 +1657,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1629,7 +1675,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1647,7 +1693,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1665,7 +1711,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1683,7 +1729,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1701,7 +1747,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1719,7 +1765,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1737,7 +1783,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1755,7 +1801,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1773,7 +1819,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1791,7 +1837,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1809,7 +1855,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1827,7 +1873,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1845,7 +1891,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1863,7 +1909,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1881,7 +1927,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1899,7 +1945,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1917,7 +1963,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1935,7 +1981,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1953,7 +1999,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1971,7 +2017,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1989,7 +2035,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2007,7 +2053,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2025,7 +2071,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2043,7 +2089,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2061,7 +2107,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2079,7 +2125,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2094,6 +2140,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2162,7 +2352,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2180,7 +2370,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2198,7 +2388,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2216,7 +2406,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2234,7 +2424,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2252,7 +2442,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2270,7 +2460,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2288,7 +2478,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2306,7 +2496,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2324,7 +2514,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2342,7 +2532,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2360,7 +2550,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2378,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2396,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2414,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2441,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2497,7 +2687,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2515,7 +2705,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2533,7 +2723,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2551,7 +2741,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2569,7 +2759,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2587,7 +2777,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2605,7 +2795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2623,7 +2813,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2641,7 +2831,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2659,7 +2849,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2677,7 +2867,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2695,7 +2885,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2713,7 +2903,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2731,7 +2921,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2749,7 +2939,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2767,7 +2957,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2785,7 +2975,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2803,7 +2993,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2821,7 +3011,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2839,7 +3029,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2857,7 +3047,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2875,7 +3065,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2893,7 +3083,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2911,7 +3101,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2929,7 +3119,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2947,7 +3137,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2965,7 +3155,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2983,7 +3173,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3001,7 +3191,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3019,7 +3209,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3037,7 +3227,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3055,7 +3245,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3073,7 +3263,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3091,7 +3281,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3109,7 +3299,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3127,7 +3317,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3142,6 +3332,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 4</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3166,7 +3500,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>06.03.2027 (lørdag) — U11 — Jarhallen</t>
+          <t>06.03.2027 (lørdag) — U11 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~100 km)</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3544,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -3228,7 +3562,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -3246,7 +3580,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3264,7 +3598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -3282,7 +3616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -3300,7 +3634,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3318,7 +3652,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3336,7 +3670,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3354,7 +3688,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3372,7 +3706,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3390,7 +3724,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3408,7 +3742,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3426,7 +3760,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3444,7 +3778,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3462,7 +3796,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3489,7 +3823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3545,7 +3879,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -3563,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -3581,7 +3915,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3599,7 +3933,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -3617,7 +3951,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -3635,7 +3969,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -3653,7 +3987,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3671,7 +4005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3689,7 +4023,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3707,7 +4041,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3725,7 +4059,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3743,7 +4077,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3761,7 +4095,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3779,7 +4113,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3797,7 +4131,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3815,7 +4149,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3833,7 +4167,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3851,7 +4185,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3869,7 +4203,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3887,7 +4221,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3905,7 +4239,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3923,7 +4257,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3941,7 +4275,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3959,7 +4293,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3977,7 +4311,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3995,7 +4329,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4013,7 +4347,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4031,7 +4365,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4049,7 +4383,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4067,7 +4401,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4085,7 +4419,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4103,7 +4437,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4121,7 +4455,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4139,7 +4473,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4157,7 +4491,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4175,7 +4509,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4190,6 +4524,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4258,7 +4736,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4276,7 +4754,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4294,7 +4772,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -4312,7 +4790,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4330,7 +4808,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4348,7 +4826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4366,7 +4844,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4384,7 +4862,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -4402,7 +4880,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4420,7 +4898,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -4438,7 +4916,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4456,7 +4934,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4474,7 +4952,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4492,7 +4970,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4510,7 +4988,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4537,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4549,7 +5027,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>18.04.2027 (søndag) — U10 — Ringerikshallen</t>
+          <t>18.04.2027 (søndag) — U10 — Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -4564,7 +5042,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~150 km)</t>
+          <t>Lengst reise: Ringerike 2 (~120 km)</t>
         </is>
       </c>
     </row>
@@ -4593,7 +5071,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4611,7 +5089,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -4629,7 +5107,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -4647,7 +5125,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -4665,7 +5143,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -4683,7 +5161,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4701,7 +5179,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4719,7 +5197,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -4737,7 +5215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4755,7 +5233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -4773,7 +5251,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4791,7 +5269,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4809,7 +5287,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4827,7 +5305,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4845,7 +5323,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4863,7 +5341,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4881,7 +5359,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4899,7 +5377,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4917,7 +5395,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4935,7 +5413,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4953,7 +5431,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4971,7 +5449,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4989,7 +5467,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5007,7 +5485,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5025,7 +5503,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -5043,7 +5521,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -5061,7 +5539,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -5079,7 +5557,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -5097,7 +5575,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5115,7 +5593,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5133,7 +5611,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5151,7 +5629,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5169,7 +5647,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5187,7 +5665,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5205,7 +5683,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5223,7 +5701,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5238,6 +5716,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5258,7 +5880,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5329,7 +5951,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5425,7 +6047,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -5457,7 +6079,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5489,7 +6111,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5553,7 +6175,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5585,7 +6207,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5681,7 +6303,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5777,7 +6399,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -5800,7 +6422,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5871,7 +6493,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -5967,7 +6589,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -5999,7 +6621,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6653,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6717,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6749,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6845,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6941,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -6334,10 +6956,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -6558,6 +7180,159 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tidspunkt på dagen velges ut fra ledig hallkapasitet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>For hver turnering beregnes hvor lang tid hele turneringen tar (rundelengde × antall runder), og planleggeren ser etter en sammenhengende ledig luke av denne lengden i vertsklubbens hallkalender. Tidspunkt nærmest 11:00 foretrekkes, for å unngå svært tidlige eller sene starttider. Hvis vertsklubbens hall ikke har en passende ledig luke den dagen, sjekkes andre klubbers haller for samme dato, og turneringen flyttes dit i stedet.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2026-09-06 (U10)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jar var opprinnelig satt opp som vert 2026-09-06, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2026-10-25 (U11)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sandefjord var opprinnelig satt opp som vert 2026-10-25, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Sandefjord Penguins i stedet.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2026-11-14 (U10)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jutul var opprinnelig satt opp som vert 2026-11-14, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2026-11-28 (U11)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Holmen var opprinnelig satt opp som vert 2026-11-28, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2027-01-09 (U11)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kongsberg var opprinnelig satt opp som vert 2027-01-09, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2027-01-16 (U10)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tønsberg var opprinnelig satt opp som vert 2027-01-16, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2027-03-06 (U11)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jar var opprinnelig satt opp som vert 2027-03-06, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Frisk Asker i stedet.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Automatisk avgjørelse</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vertsbytte 2027-04-18 (U10)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ringerike var opprinnelig satt opp som vert 2027-04-18, men hadde ingen ledig hallkapasitet av nødvendig lengde denne datoen. Turneringen ble derfor flyttet til Tønsberg i stedet.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Automatisk avgjørelse</t>
         </is>
@@ -6582,7 +7357,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6653,7 +7428,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6749,7 +7524,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6781,7 +7556,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -6845,7 +7620,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7780,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7803,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7099,7 +7874,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7970,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7227,7 +8002,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7291,7 +8066,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7355,7 +8130,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7451,7 +8226,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -7545,7 +8320,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7641,7 +8416,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7705,7 +8480,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7737,7 +8512,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -7865,7 +8640,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -7888,7 +8663,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7959,7 +8734,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8798,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8830,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8862,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8926,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8990,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8279,7 +9054,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -8302,7 +9077,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8373,7 +9148,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8469,7 +9244,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -8501,7 +9276,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8533,7 +9308,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Holmenkollen ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8597,7 +9372,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8629,7 +9404,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8725,7 +9500,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8821,7 +9596,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -8844,7 +9619,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8915,7 +9690,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -8979,7 +9754,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9786,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9850,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9882,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9267,7 +10042,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -9290,7 +10065,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9361,7 +10136,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9425,7 +10200,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -9457,7 +10232,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baerum ishall</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9521,7 +10296,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kongsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9553,7 +10328,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tonsberghallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9617,7 +10392,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jarhallen</t>
+          <t>Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9681,7 +10456,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ringerikshallen</t>
+          <t>Tonsberghallen</t>
         </is>
       </c>
     </row>
@@ -9696,7 +10471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -9708,7 +10483,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>06.09.2026 (søndag) — U10 — Jarhallen</t>
+          <t>06.09.2026 (søndag) — U10 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -9723,7 +10498,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~100 km)</t>
         </is>
       </c>
     </row>
@@ -9752,7 +10527,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -9770,7 +10545,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -9788,7 +10563,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9806,7 +10581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -9824,7 +10599,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -9842,7 +10617,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -9860,7 +10635,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -9878,7 +10653,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -9896,7 +10671,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -9914,7 +10689,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -9932,7 +10707,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -9950,7 +10725,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -9968,7 +10743,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -9986,7 +10761,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -10004,7 +10779,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -10022,7 +10797,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -10040,7 +10815,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -10058,7 +10833,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -10076,7 +10851,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -10094,7 +10869,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -10112,7 +10887,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -10130,7 +10905,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -10148,7 +10923,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -10166,7 +10941,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -10184,7 +10959,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -10202,7 +10977,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -10220,7 +10995,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -10238,7 +11013,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -10256,7 +11031,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -10274,7 +11049,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -10292,7 +11067,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -10310,7 +11085,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -10328,7 +11103,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -10346,7 +11121,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -10364,7 +11139,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -10382,7 +11157,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -10397,6 +11172,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10465,7 +11384,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -10483,7 +11402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10501,7 +11420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10519,7 +11438,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -10537,7 +11456,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10555,7 +11474,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10573,7 +11492,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10591,7 +11510,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10609,7 +11528,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10627,7 +11546,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10645,7 +11564,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10663,7 +11582,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -10681,7 +11600,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -10699,7 +11618,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -10717,7 +11636,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -10744,7 +11663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -10800,7 +11719,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -10818,7 +11737,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -10836,7 +11755,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -10854,7 +11773,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -10872,7 +11791,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -10890,7 +11809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -10908,7 +11827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -10926,7 +11845,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -10944,7 +11863,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -10962,7 +11881,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -10980,7 +11899,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -10998,7 +11917,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11016,7 +11935,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11034,7 +11953,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11052,7 +11971,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -11070,7 +11989,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -11088,7 +12007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -11106,7 +12025,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -11124,7 +12043,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -11142,7 +12061,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -11160,7 +12079,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -11178,7 +12097,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -11196,7 +12115,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -11214,7 +12133,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -11232,7 +12151,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -11250,7 +12169,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -11268,7 +12187,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -11286,7 +12205,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -11304,7 +12223,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -11322,7 +12241,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -11340,7 +12259,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -11358,7 +12277,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -11376,7 +12295,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -11394,7 +12313,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -11412,7 +12331,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -11430,7 +12349,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -11445,6 +12364,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11457,7 +12520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11469,7 +12532,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>25.10.2026 (søndag) — U11 — Sandefjord</t>
+          <t>25.10.2026 (søndag) — U11 — Sandefjord ishall</t>
         </is>
       </c>
     </row>
@@ -11481,95 +12544,84 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lengst reise: Ringerike 2 (~140 km)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Parallellbane</t>
         </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Jar 4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tønsberg 1</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar 4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jar 4</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11578,52 +12630,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Jar 4</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jar 4</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -11632,52 +12684,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Jar 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jar 4</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -11686,52 +12738,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Skien 1</t>
+          <t>Jar 4</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kongsberg 1</t>
+          <t>Skien 1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jar 4</t>
+          <t>Tønsberg 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Kongsberg 1</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -11740,37 +12792,55 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tønsberg 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Skien 1</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Kongsberg 1</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11785,7 +12855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -11797,7 +12867,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>14.11.2026 (lørdag) — U10 — Baerum ishall</t>
+          <t>14.11.2026 (lørdag) — U10 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -11812,7 +12882,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~100 km)</t>
         </is>
       </c>
     </row>
@@ -11841,7 +12911,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -11859,7 +12929,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -11877,7 +12947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -11895,7 +12965,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -11913,7 +12983,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -11931,7 +13001,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -11949,7 +13019,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -11967,7 +13037,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11985,7 +13055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -12003,7 +13073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -12021,7 +13091,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -12039,7 +13109,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -12057,7 +13127,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -12075,7 +13145,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -12093,7 +13163,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -12111,7 +13181,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12129,7 +13199,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12147,7 +13217,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12165,7 +13235,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12183,7 +13253,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12201,7 +13271,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12219,7 +13289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -12237,7 +13307,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -12255,7 +13325,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -12273,7 +13343,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -12291,7 +13361,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -12309,7 +13379,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -12327,7 +13397,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -12345,7 +13415,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -12363,7 +13433,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -12381,7 +13451,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -12399,7 +13469,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -12417,7 +13487,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -12435,7 +13505,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -12453,7 +13523,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -12471,7 +13541,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -12486,6 +13556,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12510,7 +13724,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>28.11.2026 (lørdag) — U11 — Holmenkollen ishall</t>
+          <t>28.11.2026 (lørdag) — U11 — Varner Arena</t>
         </is>
       </c>
     </row>
@@ -12525,7 +13739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~130 km)</t>
+          <t>Lengst reise: Skien 1 (~100 km)</t>
         </is>
       </c>
     </row>
@@ -12554,7 +13768,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -12572,7 +13786,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -12590,7 +13804,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -12608,7 +13822,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -12626,7 +13840,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -12644,7 +13858,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -12662,7 +13876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -12680,7 +13894,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -12698,7 +13912,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -12716,7 +13930,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -12734,7 +13948,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -12752,7 +13966,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -12770,7 +13984,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -12788,7 +14002,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -12806,7 +14020,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -12833,7 +14047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -12889,7 +14103,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -12907,7 +14121,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -12925,7 +14139,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -12943,7 +14157,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -12961,7 +14175,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -12979,7 +14193,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -12997,7 +14211,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -13015,7 +14229,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -13033,7 +14247,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -13051,7 +14265,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -13069,7 +14283,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -13087,7 +14301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -13105,7 +14319,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -13123,7 +14337,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -13141,7 +14355,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -13159,7 +14373,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -13177,7 +14391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -13195,7 +14409,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -13213,7 +14427,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -13231,7 +14445,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -13249,7 +14463,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -13267,7 +14481,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13285,7 +14499,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -13303,7 +14517,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -13321,7 +14535,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -13339,7 +14553,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -13357,7 +14571,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -13375,7 +14589,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -13393,7 +14607,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -13411,7 +14625,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -13429,7 +14643,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -13447,7 +14661,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -13465,7 +14679,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -13483,7 +14697,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -13501,7 +14715,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -13519,7 +14733,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -13534,6 +14748,150 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Jar 7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jutul 1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tønsberg 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Holmen 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Skien 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sandefjord 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kongsberg 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>(Pause)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/export/season_plan.xlsx
+++ b/export/season_plan.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skien 1 (~100 km)</t>
+          <t>Skien 1 (~109 km)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -580,7 +580,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ringerike 2 (~55 km)</t>
+          <t>Ringerike 2 (~50 km)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -619,7 +619,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skien 1 (~150 km)</t>
+          <t>Skien 1 (~147 km)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -658,7 +658,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ringerike 2 (~140 km)</t>
+          <t>Ringerike 2 (~150 km)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skien 1 (~100 km)</t>
+          <t>Skien 1 (~109 km)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skien 1 (~100 km)</t>
+          <t>Skien 1 (~109 km)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ringerike 1 (~150 km)</t>
+          <t>Ringerike 1 (~147 km)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tønsberg 1 (~80 km)</t>
+          <t>Tønsberg 1 (~82 km)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -853,7 +853,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skien 1 (~100 km)</t>
+          <t>Skien 1 (~109 km)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -892,7 +892,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kongsberg 1 (~80 km)</t>
+          <t>Kongsberg 1 (~75 km)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skien 1 (~120 km)</t>
+          <t>Skien 1 (~122 km)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skien 1 (~100 km)</t>
+          <t>Skien 1 (~109 km)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skien 1 (~120 km)</t>
+          <t>Skien 1 (~122 km)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kongsberg 1 (~60 km)</t>
+          <t>Kongsberg 1 (~62 km)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ringerike 2 (~120 km)</t>
+          <t>Ringerike 2 (~131 km)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Tønsberg 1 (~80 km)</t>
+          <t>Lengst reise: Tønsberg 1 (~82 km)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~100 km)</t>
+          <t>Lengst reise: Skien 1 (~109 km)</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Kongsberg 1 (~80 km)</t>
+          <t>Lengst reise: Kongsberg 1 (~75 km)</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~122 km)</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~100 km)</t>
+          <t>Lengst reise: Skien 1 (~109 km)</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~120 km)</t>
+          <t>Lengst reise: Skien 1 (~122 km)</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Kongsberg 1 (~60 km)</t>
+          <t>Lengst reise: Kongsberg 1 (~62 km)</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 2 (~120 km)</t>
+          <t>Lengst reise: Ringerike 2 (~131 km)</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~100 km)</t>
+          <t>Lengst reise: Skien 1 (~109 km)</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 2 (~55 km)</t>
+          <t>Lengst reise: Ringerike 2 (~50 km)</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~150 km)</t>
+          <t>Lengst reise: Skien 1 (~147 km)</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 2 (~140 km)</t>
+          <t>Lengst reise: Ringerike 2 (~150 km)</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~100 km)</t>
+          <t>Lengst reise: Skien 1 (~109 km)</t>
         </is>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Skien 1 (~100 km)</t>
+          <t>Lengst reise: Skien 1 (~109 km)</t>
         </is>
       </c>
     </row>
@@ -14074,7 +14074,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lengst reise: Ringerike 1 (~150 km)</t>
+          <t>Lengst reise: Ringerike 1 (~147 km)</t>
         </is>
       </c>
     </row>
